--- a/FPE/Graficas/tenencias/tenencia.xlsx
+++ b/FPE/Graficas/tenencias/tenencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/FPE/Graficas/tenencias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_99695F574E456261DA2FBAFC5CD81A9DF49B9741" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D02D3AB3-BC86-4B32-BB5C-53AF48B7F19B}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_99695F574E456261DA2FBAFC5CD81A9DF49B9741" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9901C750-C031-4E08-A261-D862131046C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,6 +127,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -412,6 +416,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
